--- a/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="228" documentId="11_B76429B6AEC9EAC4ECA8FFB6B29D8941586C3419" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{896CFD8B-8D9C-4936-907D-F61EDD4E79F0}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="11_B76429B6AEC9EAC4ECA8FFB6B29D8941586C3419" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22D3EEC1-F3C6-434E-A259-6A362EFF335F}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="79">
   <si>
     <t>Project ID</t>
   </si>
@@ -141,21 +144,27 @@
     <t xml:space="preserve">Nombre de ménages dans les villages ciblés, y compris les ménages dirigés par les femmes, ayant accès à l’énergie solaire </t>
   </si>
   <si>
+    <t>1500 HH</t>
+  </si>
+  <si>
     <t>Nombre de ménages dirigés par les hommes: 1200, nombre de ménages dirigés par les femmes: 300</t>
   </si>
   <si>
     <t>Environ 50 000 personnes au Total</t>
   </si>
   <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t>Nombre de nouvelles entreprises créées utilisant l’énergie solaire dans les villages ciblés par le projet</t>
+  </si>
+  <si>
+    <t>5 entreprises par village bénéficiaire, représentant 500 personnes au moins</t>
+  </si>
+  <si>
     <t>Small Enterprises</t>
   </si>
   <si>
-    <t>Nombre de nouvelles entreprises créées utilisant l’énergie solaire dans les villages ciblés par le projet</t>
-  </si>
-  <si>
-    <t>5 entreprises par village bénéficiaire, représentant 500 personnes au moins</t>
-  </si>
-  <si>
     <t>Please provide justification and numeric values in Notes. # of people per village, or per enterprise. Target values should be quantitative, with the necessary conversion factor to # of people listed in in the Notes</t>
   </si>
   <si>
@@ -220,9 +229,6 @@
   </si>
   <si>
     <t>Market Development</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
   </si>
   <si>
     <t>Support for the development of medium enterprises in the energy transition market</t>
@@ -705,6 +711,87 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -771,89 +858,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1175,61 +1181,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="79" t="s">
+      <c r="D1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="79" t="s">
+      <c r="E1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="79" t="s">
+      <c r="F1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="81" t="s">
+      <c r="H1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="83" t="s">
+      <c r="J1" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="83" t="s">
+      <c r="L1" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="83" t="s">
+      <c r="M1" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="83" t="s">
+      <c r="N1" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="83" t="s">
+      <c r="O1" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="83" t="s">
+      <c r="P1" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="83" t="s">
+      <c r="Q1" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="83" t="s">
+      <c r="R1" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="83" t="s">
+      <c r="S1" s="61" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="49"/>
@@ -1250,40 +1256,40 @@
       <c r="E2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="85">
+      <c r="G2" s="63">
         <v>0</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="J2" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="89">
+      <c r="K2" s="66">
         <v>0.24</v>
       </c>
-      <c r="L2" s="88" t="s">
+      <c r="L2" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88" t="s">
+      <c r="M2" s="65"/>
+      <c r="N2" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="103" t="s">
+      <c r="O2" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="103" t="s">
+      <c r="P2" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
     </row>
     <row r="3" spans="1:20" ht="45.75">
       <c r="A3" s="41"/>
@@ -1291,40 +1297,40 @@
       <c r="C3" s="47"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
-      <c r="F3" s="90" t="s">
+      <c r="F3" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="91">
+      <c r="G3" s="68">
         <v>0</v>
       </c>
-      <c r="H3" s="92">
+      <c r="H3" s="69">
         <v>460</v>
       </c>
-      <c r="I3" s="87" t="s">
+      <c r="I3" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="88" t="s">
+      <c r="J3" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88" t="s">
+      <c r="K3" s="65"/>
+      <c r="L3" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="93" t="s">
+      <c r="M3" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="88" t="s">
+      <c r="N3" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="103" t="s">
+      <c r="O3" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="103" t="s">
+      <c r="P3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:20" ht="45.75">
       <c r="A4" s="42"/>
@@ -1332,40 +1338,40 @@
       <c r="C4" s="48"/>
       <c r="D4" s="42"/>
       <c r="E4" s="42"/>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="91">
+      <c r="G4" s="68">
         <v>0</v>
       </c>
-      <c r="H4" s="92">
+      <c r="H4" s="69">
         <v>460</v>
       </c>
-      <c r="I4" s="87" t="s">
+      <c r="I4" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="88" t="s">
+      <c r="J4" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="K4" s="65"/>
+      <c r="L4" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="93" t="s">
+      <c r="M4" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="88" t="s">
+      <c r="N4" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="103" t="s">
+      <c r="O4" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="103" t="s">
+      <c r="P4" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="88"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
     </row>
     <row r="5" spans="1:20" ht="49.5" customHeight="1">
       <c r="A5" s="31">
@@ -1383,123 +1389,121 @@
       <c r="E5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="95">
+      <c r="G5" s="72">
         <v>0</v>
       </c>
-      <c r="H5" s="96">
-        <v>1500</v>
-      </c>
-      <c r="I5" s="97" t="s">
+      <c r="H5" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="88" t="s">
+      <c r="I5" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88" t="s">
+      <c r="K5" s="65"/>
+      <c r="L5" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88" t="s">
+      <c r="M5" s="65"/>
+      <c r="N5" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="103" t="s">
+      <c r="O5" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="103" t="s">
+      <c r="P5" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q5" s="88"/>
-      <c r="R5" s="88"/>
-      <c r="S5" s="88"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="30.75">
       <c r="A6" s="32"/>
       <c r="B6" s="35"/>
       <c r="C6" s="38"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="98" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="99">
+      <c r="E6" s="56"/>
+      <c r="F6" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="76">
         <v>10</v>
       </c>
-      <c r="H6" s="100">
+      <c r="H6" s="77">
         <v>50000</v>
       </c>
-      <c r="I6" s="101" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="88" t="s">
+      <c r="I6" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88" t="s">
+      <c r="K6" s="65"/>
+      <c r="L6" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88" t="s">
+      <c r="M6" s="65"/>
+      <c r="N6" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="103" t="s">
+      <c r="O6" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="103" t="s">
+      <c r="P6" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
-      <c r="S6" s="88"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
     </row>
     <row r="7" spans="1:20" ht="45.75">
       <c r="A7" s="33"/>
       <c r="B7" s="36"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="102" t="s">
+      <c r="D7" s="54"/>
+      <c r="E7" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="101">
+      <c r="F7" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="78">
         <v>0</v>
       </c>
-      <c r="H7" s="77">
-        <v>50</v>
-      </c>
-      <c r="I7" s="97" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="88" t="s">
+      <c r="H7" s="55">
+        <v>250</v>
+      </c>
+      <c r="I7" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88" t="s">
+      <c r="K7" s="65"/>
+      <c r="L7" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88" t="s">
+      <c r="M7" s="65"/>
+      <c r="N7" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="O7" s="103" t="s">
+      <c r="O7" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="103" t="s">
+      <c r="P7" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
-      <c r="S7" s="88"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="C10" s="27" t="s">
-        <v>41</v>
-      </c>
+      <c r="C10" s="27"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1615,19 +1619,19 @@
       <c r="T1" s="49"/>
     </row>
     <row r="2" spans="1:20" ht="45.75">
-      <c r="A2" s="56">
+      <c r="A2" s="83">
         <v>117913</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="83">
         <v>3459600</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="83" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -1659,11 +1663,11 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="45.75">
-      <c r="A3" s="57"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
       <c r="F3" s="9" t="s">
         <v>29</v>
       </c>
@@ -1693,11 +1697,11 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="45.75">
-      <c r="A4" s="58"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
       <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
@@ -1738,19 +1742,19 @@
       <c r="I5" s="17"/>
     </row>
     <row r="6" spans="1:20" ht="49.5" customHeight="1">
-      <c r="A6" s="54">
+      <c r="A6" s="81">
         <v>134793</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="81">
         <v>1431552</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="81" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="22" t="s">
@@ -1763,7 +1767,7 @@
         <v>1500</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
         <v>25</v>
@@ -1779,13 +1783,13 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="65"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="55"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="82"/>
       <c r="F7" s="52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="14">
         <v>10</v>
@@ -1794,7 +1798,7 @@
         <v>50000</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
@@ -1810,15 +1814,15 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="45.75">
-      <c r="A8" s="55"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="55"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="82"/>
       <c r="E8" s="53" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -1827,7 +1831,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -1844,7 +1848,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="C11" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1941,19 +1945,19 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.75">
-      <c r="A2" s="56">
+      <c r="A2" s="83">
         <v>117913</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="56">
+      <c r="D2" s="83">
         <v>3459600</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="83" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="23" t="s">
@@ -1970,11 +1974,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.75">
-      <c r="A3" s="57"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
       <c r="F3" s="9" t="s">
         <v>29</v>
       </c>
@@ -1990,11 +1994,11 @@
       <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10" ht="45.75">
-      <c r="A4" s="58"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
       <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
@@ -2022,19 +2026,19 @@
       <c r="J5" s="26"/>
     </row>
     <row r="6" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A6" s="54">
+      <c r="A6" s="81">
         <v>134793</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="81">
         <v>1431552</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="81" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="22" t="s">
@@ -2047,18 +2051,18 @@
         <v>1500</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" s="26"/>
     </row>
     <row r="7" spans="1:10" ht="37.5">
-      <c r="A7" s="65"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
       <c r="F7" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="14">
         <v>10</v>
@@ -2067,18 +2071,18 @@
         <v>50</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" s="26"/>
     </row>
     <row r="8" spans="1:10" ht="45.75">
-      <c r="A8" s="55"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
       <c r="F8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="12">
         <v>0</v>
@@ -2087,13 +2091,13 @@
         <v>50</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J8" s="26"/>
     </row>
     <row r="11" spans="1:10">
       <c r="C11" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2139,160 +2143,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="72" t="s">
-        <v>45</v>
+      <c r="A2" s="99" t="s">
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="72"/>
+      <c r="A3" s="99"/>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="72"/>
+      <c r="A4" s="99"/>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="73" t="s">
-        <v>51</v>
+      <c r="A5" s="100" t="s">
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="73"/>
+      <c r="A6" s="100"/>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="73"/>
+      <c r="A7" s="100"/>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="73"/>
+      <c r="A8" s="100"/>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="73"/>
+      <c r="A9" s="100"/>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="74" t="s">
-        <v>62</v>
+      <c r="A10" s="101" t="s">
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="74"/>
+      <c r="A11" s="101"/>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="75" t="s">
-        <v>66</v>
+      <c r="A12" s="102" t="s">
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="75"/>
+      <c r="A13" s="102"/>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="75"/>
+      <c r="A14" s="102"/>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2307,15 +2311,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2363,7 +2358,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2612,14 +2607,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0451E445-12D4-4325-B162-D7FA49EAECE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{728D47DB-CBAC-4C36-A531-450D68A66E30}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{728D47DB-CBAC-4C36-A531-450D68A66E30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78A0F9A-F97D-42D3-9953-2DB2087995FA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78A0F9A-F97D-42D3-9953-2DB2087995FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0451E445-12D4-4325-B162-D7FA49EAECE6}"/>
 </file>
--- a/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_B76429B6AEC9EAC4ECA8FFB6B29D8941586C3419" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD6BE568-3251-4BAE-B658-5DCE8FCD1A73}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="11_B76429B6AEC9EAC4ECA8FFB6B29D8941586C3419" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBB40951-36D8-4486-AF58-76B4957F669C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="97">
   <si>
     <t>Project ID</t>
   </si>
@@ -123,9 +123,15 @@
     <t>Non-VF</t>
   </si>
   <si>
+    <t>Just</t>
+  </si>
+  <si>
     <t>Close the gap on energy access</t>
   </si>
   <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
     <t>Solar</t>
   </si>
   <si>
@@ -135,9 +141,18 @@
     <t>Il ya 576 productrices de chanbons qui ont été recensées dans 16 villages</t>
   </si>
   <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Clean Cooking</t>
+  </si>
+  <si>
     <t>Pourcentatge des femmes productrices de charbon reconverties à d'autres activités génératrices de revenus</t>
   </si>
   <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
     <t>Accès aux énergies renouvelables en milieu rural au Togo</t>
   </si>
   <si>
@@ -153,6 +168,9 @@
     <t>Nombre de ménages dirigés par les hommes: 1200, nombre de ménages dirigés par les femmes: 300</t>
   </si>
   <si>
+    <t>Nombre de personnes bénéficiant des services de l'énergie solaire</t>
+  </si>
+  <si>
     <t>Environ 50 000 personnes au Total</t>
   </si>
   <si>
@@ -165,6 +183,18 @@
     <t>5 entreprises par village bénéficiaire, représentant 500 personnes au moins</t>
   </si>
   <si>
+    <t>Projet de développement des terroirs villageois sobres en carbone et résilients aux changements climatiques</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/01002293</t>
+  </si>
+  <si>
+    <t>Nombre additionnel de ménages dirigés par les femmes dans les écovillages ayant accès à l’énergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350 ménages additionnels dans les écovillages ont accès à l'énergie solaire en plus des 200 ménages déjà existants  </t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -193,9 +223,6 @@
   </si>
   <si>
     <t>Number of MW installed capacity</t>
-  </si>
-  <si>
-    <t>Clean Cooking</t>
   </si>
   <si>
     <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
@@ -304,7 +331,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +430,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -536,17 +571,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -589,15 +613,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -678,9 +714,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -727,7 +760,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -781,19 +814,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -814,69 +841,92 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -888,8 +938,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1215,204 +1266,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="80" t="s">
+      <c r="L1" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="81" t="s">
+      <c r="M1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="80" t="s">
+      <c r="N1" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="80" t="s">
+      <c r="O1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="81" t="s">
+      <c r="P1" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="81" t="s">
+      <c r="Q1" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="82" t="s">
+      <c r="R1" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="83" t="s">
+      <c r="S1" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="82" t="s">
+      <c r="T1" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="83" t="s">
+      <c r="U1" s="80" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="45.75">
-      <c r="A2" s="37">
+      <c r="A2" s="36">
         <v>117913</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="36">
         <v>3459600</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="59">
         <v>0</v>
       </c>
-      <c r="H2" s="76" t="s">
+      <c r="H2" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="61" t="s">
+      <c r="I2" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="63">
+      <c r="K2" s="62">
         <v>0.24</v>
       </c>
-      <c r="L2" s="84" t="s">
+      <c r="L2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="77"/>
-      <c r="N2" s="85" t="s">
+      <c r="M2" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="62" t="s">
+      <c r="N2" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="77"/>
-      <c r="U2" s="62"/>
+      <c r="O2" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="74"/>
+      <c r="U2" s="61"/>
     </row>
     <row r="3" spans="1:21" ht="45.75">
-      <c r="A3" s="38"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="65">
+      <c r="A3" s="37"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="64">
         <v>0</v>
       </c>
-      <c r="H3" s="66">
+      <c r="H3" s="65">
         <v>460</v>
       </c>
-      <c r="I3" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="62" t="s">
+      <c r="I3" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="62"/>
-      <c r="L3" s="84" t="s">
+      <c r="K3" s="61"/>
+      <c r="L3" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="77"/>
-      <c r="N3" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="62"/>
+      <c r="M3" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="61"/>
     </row>
     <row r="4" spans="1:21" ht="45.75">
-      <c r="A4" s="39"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="65">
+      <c r="A4" s="38"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="64">
         <v>0</v>
       </c>
-      <c r="H4" s="66">
+      <c r="H4" s="65">
         <v>460</v>
       </c>
-      <c r="I4" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="62" t="s">
+      <c r="I4" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="84" t="s">
+      <c r="K4" s="61"/>
+      <c r="L4" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="77"/>
-      <c r="N4" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="62"/>
+      <c r="M4" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="61"/>
     </row>
     <row r="5" spans="1:21" ht="49.5" customHeight="1">
       <c r="A5" s="28">
         <v>134793</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>40</v>
       </c>
       <c r="D5" s="28">
         <v>1431552</v>
@@ -1420,116 +1483,185 @@
       <c r="E5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="68">
+      <c r="F5" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="67">
         <v>0</v>
       </c>
-      <c r="H5" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="62" t="s">
+      <c r="H5" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="63">
+      <c r="K5" s="62">
         <v>0.2</v>
       </c>
-      <c r="L5" s="84" t="s">
+      <c r="L5" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="77"/>
-      <c r="N5" s="85" t="s">
+      <c r="M5" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="62" t="s">
+      <c r="N5" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="77"/>
-      <c r="U5" s="62"/>
+      <c r="O5" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="74"/>
+      <c r="U5" s="61"/>
     </row>
     <row r="6" spans="1:21" ht="45.75">
       <c r="A6" s="29"/>
       <c r="B6" s="32"/>
-      <c r="C6" s="35"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="29"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="71" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="72">
-        <v>10</v>
-      </c>
-      <c r="H6" s="73">
+      <c r="E6" s="52"/>
+      <c r="F6" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="67">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="70">
         <v>50000</v>
       </c>
-      <c r="I6" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="62" t="s">
+      <c r="I6" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="62"/>
-      <c r="L6" s="84" t="s">
+      <c r="K6" s="61"/>
+      <c r="L6" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="77"/>
-      <c r="N6" s="85" t="s">
+      <c r="M6" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="62"/>
+      <c r="N6" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="61"/>
     </row>
     <row r="7" spans="1:21" ht="45.75">
       <c r="A7" s="30"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="74">
+      <c r="C7" s="35"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="71">
         <v>0</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="51">
         <v>250</v>
       </c>
-      <c r="I7" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="62" t="s">
+      <c r="I7" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="62"/>
-      <c r="L7" s="84" t="s">
+      <c r="K7" s="104"/>
+      <c r="L7" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="85" t="s">
+      <c r="M7" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="62"/>
+      <c r="N7" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" s="104"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="104"/>
+    </row>
+    <row r="8" spans="1:21" ht="106.5">
+      <c r="A8" s="29">
+        <v>1002293</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="69">
+        <v>200</v>
+      </c>
+      <c r="H8" s="69">
+        <v>550</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="102">
+        <v>1</v>
+      </c>
+      <c r="L8" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
     </row>
     <row r="10" spans="1:21">
       <c r="C10" s="24"/>
@@ -1539,40 +1671,41 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T8:T10" xr:uid="{B1D5A021-84BC-4689-999E-3FB27BF4D958}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q7 S8:S10" xr:uid="{A50CD785-3A8C-47B3-B7F5-CACEB8C42B33}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q7 S9:S10" xr:uid="{A50CD785-3A8C-47B3-B7F5-CACEB8C42B33}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P7 R8:R10" xr:uid="{ED5BBE8A-78E6-46A3-9985-86931D7D9CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P7 R9:R10" xr:uid="{ED5BBE8A-78E6-46A3-9985-86931D7D9CD0}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P8:Q10" xr:uid="{796B4526-AE9E-4442-846E-0AAF85AA766C}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O8:O10 N2:N7" xr:uid="{F23DB627-7883-4DBE-A97F-8BF07F256900}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N8 O9:O10" xr:uid="{F23DB627-7883-4DBE-A97F-8BF07F256900}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O7" xr:uid="{2F52C8F9-19F4-496F-8AF3-348859AA1053}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{2F52C8F9-19F4-496F-8AF3-348859AA1053}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M7" xr:uid="{543F76BF-6406-4500-97CB-E080CD4E9C2C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M8" xr:uid="{543F76BF-6406-4500-97CB-E080CD4E9C2C}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T7" xr:uid="{9D7BB4E0-4B8A-4F58-B575-22BA9D556258}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L7" xr:uid="{91F8ADFF-95C3-4781-8D06-5ABBC5824D3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L8" xr:uid="{91F8ADFF-95C3-4781-8D06-5ABBC5824D3E}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R7" xr:uid="{75891C2E-4F74-46FB-8BD2-E3D3A00AAB6E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{75891C2E-4F74-46FB-8BD2-E3D3A00AAB6E}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S7" xr:uid="{CB8CC6D2-C673-4017-AA60-2F65AF4BC053}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{CB8CC6D2-C673-4017-AA60-2F65AF4BC053}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{A5C1D4D0-7D49-4CB0-BB2E-F49E77CA0C94}"/>
     <hyperlink ref="C5" r:id="rId2" xr:uid="{A312BDC0-7C26-40A1-AE80-9C9DE94C21CD}"/>
+    <hyperlink ref="C8" r:id="rId3" xr:uid="{1CC717D9-47E8-439D-B761-EC5CE50665D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1639,52 +1772,52 @@
       <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="46" t="s">
+      <c r="L1" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="P1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="Q1" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="46" t="s">
+      <c r="R1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="46" t="s">
+      <c r="S1" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="45"/>
     </row>
     <row r="2" spans="1:20" ht="45.75">
-      <c r="A2" s="88">
+      <c r="A2" s="86">
         <v>117913</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="88">
+      <c r="D2" s="86">
         <v>3459600</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="86" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="20" t="s">
@@ -1702,27 +1835,27 @@
       <c r="J2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="47">
+      <c r="K2" s="46">
         <v>0.24</v>
       </c>
       <c r="L2" t="s">
         <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="45.75">
-      <c r="A3" s="89"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="25">
         <v>0</v>
@@ -1731,7 +1864,7 @@
         <v>460</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
@@ -1739,24 +1872,24 @@
       <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="48" t="s">
-        <v>46</v>
+      <c r="M3" s="47" t="s">
+        <v>56</v>
       </c>
       <c r="O3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="45.75">
-      <c r="A4" s="90"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
       <c r="F4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4" s="27">
         <v>0</v>
@@ -1765,7 +1898,7 @@
         <v>460</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
         <v>27</v>
@@ -1773,11 +1906,11 @@
       <c r="L4" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="48" t="s">
-        <v>46</v>
+      <c r="M4" s="47" t="s">
+        <v>56</v>
       </c>
       <c r="O4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P4" t="s">
         <v>23</v>
@@ -1795,23 +1928,23 @@
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:20" ht="49.5" customHeight="1">
-      <c r="A6" s="86">
+      <c r="A6" s="84">
         <v>134793</v>
       </c>
-      <c r="B6" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="101" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="86">
+      <c r="B6" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="84">
         <v>1431552</v>
       </c>
-      <c r="E6" s="86" t="s">
+      <c r="E6" s="84" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
@@ -1820,7 +1953,7 @@
         <v>1500</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>27</v>
@@ -1829,20 +1962,20 @@
         <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="97"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="49" t="s">
-        <v>39</v>
+      <c r="A7" s="95"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="48" t="s">
+        <v>45</v>
       </c>
       <c r="G7" s="11">
         <v>10</v>
@@ -1851,7 +1984,7 @@
         <v>50000</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
@@ -1860,22 +1993,22 @@
         <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45.75">
-      <c r="A8" s="87"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="50" t="s">
+      <c r="A8" s="85"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -1884,7 +2017,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J8" t="s">
         <v>27</v>
@@ -1893,7 +2026,7 @@
         <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P8" t="s">
         <v>23</v>
@@ -1901,7 +2034,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="C11" s="24" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1998,19 +2131,19 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="45.75">
-      <c r="A2" s="88">
+      <c r="A2" s="86">
         <v>117913</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="88">
+      <c r="D2" s="86">
         <v>3459600</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="86" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="20" t="s">
@@ -2027,13 +2160,13 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.75">
-      <c r="A3" s="89"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="25">
         <v>0</v>
@@ -2042,18 +2175,18 @@
         <v>460</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3" s="23"/>
     </row>
     <row r="4" spans="1:10" ht="45.75">
-      <c r="A4" s="90"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
       <c r="F4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4" s="27">
         <v>0</v>
@@ -2062,7 +2195,7 @@
         <v>460</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" s="23"/>
     </row>
@@ -2079,23 +2212,23 @@
       <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A6" s="86">
+      <c r="A6" s="84">
         <v>134793</v>
       </c>
-      <c r="B6" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="101" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="86">
+      <c r="B6" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="84">
         <v>1431552</v>
       </c>
-      <c r="E6" s="86" t="s">
+      <c r="E6" s="84" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
@@ -2104,18 +2237,18 @@
         <v>1500</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" spans="1:10" ht="37.5">
-      <c r="A7" s="97"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G7" s="11">
         <v>10</v>
@@ -2124,18 +2257,18 @@
         <v>50</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10" ht="45.75">
-      <c r="A8" s="87"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
       <c r="F8" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -2144,27 +2277,27 @@
         <v>50</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="11" spans="1:10">
       <c r="C11" s="24" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2195,179 +2328,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="75" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>50</v>
+      <c r="B2" s="76" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="104" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="79" t="s">
-        <v>52</v>
+      <c r="A3" s="110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="79" t="s">
-        <v>54</v>
+      <c r="A4" s="110" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="104" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="79" t="s">
-        <v>56</v>
+      <c r="A5" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="76" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="110" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="110" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="111" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="110" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="111" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="110" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="111" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="110" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="111" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="110" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="111" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="104" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="79" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="104" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="79" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="104" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="79" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="104" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="105" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="104" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="79" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="105" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="104" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="105" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="104" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="105" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="104" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="105" t="s">
-        <v>76</v>
+      <c r="B16" s="111" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="104" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="79" t="s">
-        <v>78</v>
+      <c r="A17" s="110" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="104" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="105" t="s">
-        <v>80</v>
+      <c r="A18" s="110" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="111" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="104" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="105" t="s">
-        <v>82</v>
+      <c r="A19" s="110" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="111" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="104" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="105" t="s">
-        <v>84</v>
+      <c r="A20" s="110" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="111" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="104" t="s">
+      <c r="A21" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="106" t="s">
-        <v>85</v>
+      <c r="B21" s="112" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="105" t="s">
-        <v>87</v>
+      <c r="A22" s="110" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="111" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2376,17 +2509,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2411,6 +2535,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2490,6 +2615,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2633,6 +2763,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2676,17 +2815,22 @@
         <AccountId>772</AccountId>
         <AccountType/>
       </UserInfo>
+      <UserInfo>
+        <DisplayName>Aki Kogachi</DisplayName>
+        <AccountId>2532</AccountId>
+        <AccountType/>
+      </UserInfo>
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0451E445-12D4-4325-B162-D7FA49EAECE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F69302E-DA0C-4D38-9120-6077AA4137F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78A0F9A-F97D-42D3-9953-2DB2087995FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0451E445-12D4-4325-B162-D7FA49EAECE6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Togo - Energy Projects.xlsx
@@ -329,7 +329,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -636,17 +636,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -750,6 +756,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1397,15 +1443,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K5" s="64" t="n">
+      <c r="K5" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="114" t="n"/>
-      <c r="M5" s="115" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L5" s="115" t="n"/>
+      <c r="M5" s="60" t="n"/>
       <c r="N5" s="61" t="n"/>
       <c r="O5" s="61" t="n"/>
       <c r="P5" s="74" t="n"/>
@@ -1635,15 +1677,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K9" s="71" t="n">
+      <c r="K9" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="116" t="n"/>
-      <c r="M9" s="115" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L9" s="117" t="n"/>
+      <c r="M9" s="69" t="n"/>
       <c r="N9" s="104" t="n"/>
       <c r="O9" s="104" t="n"/>
       <c r="P9" s="106" t="n"/>
@@ -1671,9 +1709,9 @@
         </is>
       </c>
       <c r="D10" s="95" t="n"/>
-      <c r="E10" s="117" t="n"/>
-      <c r="F10" s="117" t="n"/>
-      <c r="G10" s="117" t="n"/>
+      <c r="E10" s="118" t="n"/>
+      <c r="F10" s="118" t="n"/>
+      <c r="G10" s="118" t="n"/>
       <c r="H10" s="95" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -1757,15 +1795,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="69" t="n">
+      <c r="K11" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="115" t="n"/>
-      <c r="M11" s="115" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L11" s="119" t="n"/>
+      <c r="M11" s="69" t="n"/>
       <c r="N11" s="14" t="n"/>
       <c r="O11" s="102" t="n"/>
       <c r="P11" s="74" t="n"/>
@@ -1783,7 +1817,7 @@
       <c r="C13" s="24" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="14">
+  <dataValidations count="12">
     <dataValidation sqref="T8:T10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -1820,17 +1854,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1952,23 +1981,23 @@
       <c r="T1" s="45" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="118" t="n">
+      <c r="A2" s="120" t="n">
         <v>117913</v>
       </c>
-      <c r="B2" s="119" t="inlineStr">
+      <c r="B2" s="121" t="inlineStr">
         <is>
           <t>Résilience des communautés et des écosystèmes</t>
         </is>
       </c>
-      <c r="C2" s="120" t="inlineStr">
+      <c r="C2" s="122" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00117913</t>
         </is>
       </c>
-      <c r="D2" s="118" t="n">
+      <c r="D2" s="120" t="n">
         <v>3459600</v>
       </c>
-      <c r="E2" s="118" t="inlineStr">
+      <c r="E2" s="120" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
@@ -2016,11 +2045,11 @@
       </c>
     </row>
     <row r="3" ht="45.75" customHeight="1">
-      <c r="A3" s="121" t="n"/>
-      <c r="B3" s="121" t="n"/>
-      <c r="C3" s="121" t="n"/>
-      <c r="D3" s="121" t="n"/>
-      <c r="E3" s="121" t="n"/>
+      <c r="A3" s="123" t="n"/>
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="123" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Pourcentage des producteurs de charbon dans les localités cibles utilisant des techniques efficientes de carbonisation du bois avec un rendement supérieur à 30%</t>
@@ -2064,11 +2093,11 @@
       </c>
     </row>
     <row r="4" ht="45.75" customHeight="1">
-      <c r="A4" s="122" t="n"/>
-      <c r="B4" s="122" t="n"/>
-      <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="n"/>
-      <c r="E4" s="122" t="n"/>
+      <c r="A4" s="124" t="n"/>
+      <c r="B4" s="124" t="n"/>
+      <c r="C4" s="124" t="n"/>
+      <c r="D4" s="124" t="n"/>
+      <c r="E4" s="124" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Pourcentatge des femmes productrices de charbon reconverties à d'autres activités génératrices de revenus</t>
@@ -2123,23 +2152,23 @@
       <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="49.5" customHeight="1">
-      <c r="A6" s="123" t="n">
+      <c r="A6" s="125" t="n">
         <v>134793</v>
       </c>
-      <c r="B6" s="124" t="inlineStr">
+      <c r="B6" s="126" t="inlineStr">
         <is>
           <t>Accès aux énergies renouvelables en milieu rural au Togo</t>
         </is>
       </c>
-      <c r="C6" s="125" t="inlineStr">
+      <c r="C6" s="127" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00134793</t>
         </is>
       </c>
-      <c r="D6" s="123" t="n">
+      <c r="D6" s="125" t="n">
         <v>1431552</v>
       </c>
-      <c r="E6" s="123" t="inlineStr">
+      <c r="E6" s="125" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
@@ -2182,11 +2211,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="121" t="n"/>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
-      <c r="D7" s="121" t="n"/>
-      <c r="E7" s="122" t="n"/>
+      <c r="A7" s="123" t="n"/>
+      <c r="B7" s="123" t="n"/>
+      <c r="C7" s="123" t="n"/>
+      <c r="D7" s="123" t="n"/>
+      <c r="E7" s="124" t="n"/>
       <c r="F7" s="48" t="inlineStr">
         <is>
           <t>Environ 50 000 personnes au Total</t>
@@ -2225,10 +2254,10 @@
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="122" t="n"/>
-      <c r="B8" s="122" t="n"/>
-      <c r="C8" s="122" t="n"/>
-      <c r="D8" s="122" t="n"/>
+      <c r="A8" s="124" t="n"/>
+      <c r="B8" s="124" t="n"/>
+      <c r="C8" s="124" t="n"/>
+      <c r="D8" s="124" t="n"/>
       <c r="E8" s="49" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
@@ -2382,23 +2411,23 @@
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="118" t="n">
+      <c r="A2" s="120" t="n">
         <v>117913</v>
       </c>
-      <c r="B2" s="119" t="inlineStr">
+      <c r="B2" s="121" t="inlineStr">
         <is>
           <t>Résilience des communautés et des écosystèmes</t>
         </is>
       </c>
-      <c r="C2" s="120" t="inlineStr">
+      <c r="C2" s="122" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00117913</t>
         </is>
       </c>
-      <c r="D2" s="118" t="n">
+      <c r="D2" s="120" t="n">
         <v>3459600</v>
       </c>
-      <c r="E2" s="118" t="inlineStr">
+      <c r="E2" s="120" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
@@ -2421,11 +2450,11 @@
       </c>
     </row>
     <row r="3" ht="45.75" customHeight="1">
-      <c r="A3" s="121" t="n"/>
-      <c r="B3" s="121" t="n"/>
-      <c r="C3" s="121" t="n"/>
-      <c r="D3" s="121" t="n"/>
-      <c r="E3" s="121" t="n"/>
+      <c r="A3" s="123" t="n"/>
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="123" t="n"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Pourcentage des producteurs de charbon dans les localités cibles utilisant des techniques efficientes de carbonisation du bois avec un rendement supérieur à 30%</t>
@@ -2445,11 +2474,11 @@
       <c r="J3" s="23" t="n"/>
     </row>
     <row r="4" ht="45.75" customHeight="1">
-      <c r="A4" s="122" t="n"/>
-      <c r="B4" s="122" t="n"/>
-      <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="n"/>
-      <c r="E4" s="122" t="n"/>
+      <c r="A4" s="124" t="n"/>
+      <c r="B4" s="124" t="n"/>
+      <c r="C4" s="124" t="n"/>
+      <c r="D4" s="124" t="n"/>
+      <c r="E4" s="124" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Pourcentatge des femmes productrices de charbon reconverties à d'autres activités génératrices de revenus</t>
@@ -2481,23 +2510,23 @@
       <c r="J5" s="23" t="n"/>
     </row>
     <row r="6" ht="49.5" customHeight="1">
-      <c r="A6" s="123" t="n">
+      <c r="A6" s="125" t="n">
         <v>134793</v>
       </c>
-      <c r="B6" s="124" t="inlineStr">
+      <c r="B6" s="126" t="inlineStr">
         <is>
           <t>Accès aux énergies renouvelables en milieu rural au Togo</t>
         </is>
       </c>
-      <c r="C6" s="125" t="inlineStr">
+      <c r="C6" s="127" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00134793</t>
         </is>
       </c>
-      <c r="D6" s="123" t="n">
+      <c r="D6" s="125" t="n">
         <v>1431552</v>
       </c>
-      <c r="E6" s="123" t="inlineStr">
+      <c r="E6" s="125" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
@@ -2521,11 +2550,11 @@
       <c r="J6" s="23" t="n"/>
     </row>
     <row r="7" ht="37.5" customHeight="1">
-      <c r="A7" s="121" t="n"/>
-      <c r="B7" s="121" t="n"/>
-      <c r="C7" s="121" t="n"/>
-      <c r="D7" s="121" t="n"/>
-      <c r="E7" s="121" t="n"/>
+      <c r="A7" s="123" t="n"/>
+      <c r="B7" s="123" t="n"/>
+      <c r="C7" s="123" t="n"/>
+      <c r="D7" s="123" t="n"/>
+      <c r="E7" s="123" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Nombre de villages additionnels bénéficiant du partenariat entre le PNUD et les acteurs du privé pour le développement des minicentrales solaires pour l’électrification et la transformation des produits agricoles</t>
@@ -2545,11 +2574,11 @@
       <c r="J7" s="23" t="n"/>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="122" t="n"/>
-      <c r="B8" s="122" t="n"/>
-      <c r="C8" s="122" t="n"/>
-      <c r="D8" s="122" t="n"/>
-      <c r="E8" s="122" t="n"/>
+      <c r="A8" s="124" t="n"/>
+      <c r="B8" s="124" t="n"/>
+      <c r="C8" s="124" t="n"/>
+      <c r="D8" s="124" t="n"/>
+      <c r="E8" s="124" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Nombre de nouvelles entreprises créées utilisant l’énergie solaire dans les villages ciblés par le projet</t>
@@ -2610,288 +2639,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="126" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="126" t="inlineStr">
+      <c r="B1" s="128" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="127" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="127" t="inlineStr">
+      <c r="B2" s="129" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="127" t="inlineStr">
+      <c r="A3" s="129" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="127" t="inlineStr">
+      <c r="B3" s="129" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="127" t="inlineStr">
+      <c r="A4" s="129" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="127" t="inlineStr">
+      <c r="B4" s="129" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="127" t="inlineStr">
+      <c r="A5" s="129" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="127" t="inlineStr">
+      <c r="B5" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="127" t="inlineStr">
+      <c r="A6" s="129" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="127" t="inlineStr">
+      <c r="B6" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="127" t="inlineStr">
+      <c r="A7" s="129" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="127" t="inlineStr">
+      <c r="B7" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="127" t="inlineStr">
+      <c r="A8" s="129" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="127" t="inlineStr">
+      <c r="B8" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="127" t="inlineStr">
+      <c r="A9" s="129" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="127" t="inlineStr">
+      <c r="B9" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="127" t="inlineStr">
+      <c r="A10" s="129" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="127" t="inlineStr">
+      <c r="B10" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="127" t="inlineStr">
+      <c r="A11" s="129" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="127" t="inlineStr">
+      <c r="B11" s="129" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="127" t="inlineStr">
+      <c r="A12" s="129" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="127" t="inlineStr">
+      <c r="B12" s="129" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="127" t="inlineStr">
+      <c r="A13" s="129" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="127" t="inlineStr">
+      <c r="B13" s="129" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="127" t="inlineStr">
+      <c r="A14" s="129" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="127" t="inlineStr">
+      <c r="B14" s="129" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="127" t="inlineStr">
+      <c r="A15" s="129" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="127" t="inlineStr">
+      <c r="B15" s="129" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="127" t="inlineStr">
+      <c r="A16" s="129" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="127" t="inlineStr">
+      <c r="B16" s="129" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="127" t="inlineStr">
+      <c r="A17" s="129" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="127" t="inlineStr">
+      <c r="B17" s="129" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="127" t="inlineStr">
+      <c r="A18" s="129" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="127" t="inlineStr">
+      <c r="B18" s="129" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="127" t="inlineStr">
+      <c r="A19" s="129" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="127" t="inlineStr">
+      <c r="B19" s="129" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="127" t="inlineStr">
+      <c r="A20" s="129" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="127" t="inlineStr">
+      <c r="B20" s="129" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="127" t="inlineStr">
+      <c r="A21" s="129" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="127" t="inlineStr">
+      <c r="B21" s="129" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="127" t="inlineStr">
+      <c r="A22" s="129" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="127" t="inlineStr">
+      <c r="B22" s="129" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="127" t="inlineStr">
+      <c r="A23" s="129" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="127" t="inlineStr">
+      <c r="B23" s="129" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="127" t="inlineStr">
+      <c r="A24" s="129" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="127" t="inlineStr">
+      <c r="B24" s="129" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
